--- a/CATALOGO 2026 GLOP.xlsx
+++ b/CATALOGO 2026 GLOP.xlsx
@@ -191,6 +191,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -211,6 +212,7 @@
       <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -255,16 +257,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -394,468 +400,468 @@
   <dimension ref="B2:K16"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.73"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>2018</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="2" t="n">
         <v>6.45</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I3" s="2" t="n">
         <v>9.2</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="2" t="n">
         <v>11.75</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="I4" s="2" t="n">
         <v>16.75</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="2" t="n">
         <v>26.5</v>
       </c>
-      <c r="K4" s="0" t="s">
+      <c r="K4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="I5" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="K5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="I6" s="2" t="n">
         <v>34.9</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>54.5</v>
       </c>
-      <c r="K6" s="0" t="s">
+      <c r="K6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="I7" s="2" t="n">
         <v>68.5</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>105.5</v>
       </c>
-      <c r="K7" s="0" t="s">
+      <c r="K7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="2" t="n">
         <v>6.4</v>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="I8" s="2" t="n">
         <v>8.54</v>
       </c>
-      <c r="K8" s="0" t="s">
+      <c r="K8" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="2" t="n">
         <v>6.4</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="I9" s="2" t="n">
         <v>8.54</v>
       </c>
-      <c r="K9" s="0" t="s">
+      <c r="K9" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="2" t="n">
         <v>6.4</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="2" t="n">
         <v>8.54</v>
       </c>
-      <c r="K10" s="0" t="s">
+      <c r="K10" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="2" t="n">
         <v>6.4</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="I11" s="2" t="n">
         <v>8.54</v>
       </c>
-      <c r="K11" s="0" t="s">
+      <c r="K11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="2" t="n">
         <v>9.5</v>
       </c>
-      <c r="I12" s="1" t="n">
+      <c r="I12" s="2" t="n">
         <v>12.67</v>
       </c>
-      <c r="K12" s="0" t="s">
+      <c r="K12" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="2" t="n">
         <v>19.57</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="I13" s="2" t="n">
         <v>26.11</v>
       </c>
-      <c r="K13" s="0" t="s">
+      <c r="K13" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="G14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="H14" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="I14" s="1" t="n">
+      <c r="I14" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="K14" s="0" t="s">
+      <c r="K14" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H15" s="2" t="n">
         <v>9.9</v>
       </c>
-      <c r="I15" s="1" t="n">
+      <c r="I15" s="2" t="n">
         <v>13.37</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="K15" s="0" t="s">
+      <c r="K15" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="2" t="n">
         <v>7.2</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="I16" s="2" t="n">
         <v>9.7</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="K16" s="0" t="s">
+      <c r="K16" s="1" t="s">
         <v>51</v>
       </c>
     </row>

--- a/CATALOGO 2026 GLOP.xlsx
+++ b/CATALOGO 2026 GLOP.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -191,7 +191,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -212,7 +211,6 @@
       <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -257,20 +255,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -397,471 +391,468 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:K16"/>
+  <dimension ref="A2:J16"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.73"/>
-  </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="0" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="C3" s="0" t="n">
         <v>2018</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>6.45</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="H3" s="1" t="n">
         <v>9.2</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="I3" s="1" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="J3" s="0" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="C4" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="E4" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="F4" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>11.75</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="H4" s="1" t="n">
         <v>16.75</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="I4" s="1" t="n">
         <v>26.5</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="J4" s="0" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="C5" s="0" t="n">
         <v>2023</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="F5" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>16.2</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="H5" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="I5" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="J5" s="0" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="C6" s="0" t="n">
         <v>2016</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="E6" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="F6" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>24.5</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="H6" s="1" t="n">
         <v>34.9</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="I6" s="1" t="n">
         <v>54.5</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="J6" s="0" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="C7" s="0" t="n">
         <v>2014</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="F7" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="H7" s="1" t="n">
         <v>68.5</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="I7" s="1" t="n">
         <v>105.5</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="0" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="C8" s="0" t="n">
         <v>2025</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="E8" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="F8" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="G8" s="1" t="n">
         <v>6.4</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="H8" s="1" t="n">
         <v>8.54</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" s="0" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="B9" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="C9" s="0" t="n">
         <v>2024</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="E9" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="F9" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="G9" s="1" t="n">
         <v>6.4</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="H9" s="1" t="n">
         <v>8.54</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="J9" s="0" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="C10" s="0" t="n">
         <v>2023</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="D10" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="E10" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="F10" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="G10" s="1" t="n">
         <v>6.4</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="H10" s="1" t="n">
         <v>8.54</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="J10" s="0" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="C11" s="0" t="n">
         <v>2023</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="E11" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="F11" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="G11" s="1" t="n">
         <v>6.4</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="H11" s="1" t="n">
         <v>8.54</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="J11" s="0" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="C12" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="E12" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="F12" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="G12" s="1" t="n">
         <v>9.5</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="H12" s="1" t="n">
         <v>12.67</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="J12" s="0" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
+      <c r="A13" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="C13" s="0" t="n">
         <v>2021</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="E13" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="F13" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="G13" s="1" t="n">
         <v>19.57</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="H13" s="1" t="n">
         <v>26.11</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="J13" s="0" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="C14" s="0" t="n">
         <v>2022</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="E14" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="F14" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="G14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="H14" s="1" t="n">
         <v>16.2</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="I14" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="J14" s="0" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="C15" s="0" t="n">
         <v>2024</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="E15" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="F15" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="G15" s="1" t="n">
         <v>9.9</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="H15" s="1" t="n">
         <v>13.37</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="I15" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="0" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="B16" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="C16" s="0" t="n">
         <v>2025</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="E16" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="F16" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="G16" s="1" t="n">
         <v>7.2</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="H16" s="1" t="n">
         <v>9.7</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="I16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="J16" s="0" t="s">
         <v>51</v>
       </c>
     </row>

--- a/CATALOGO 2026 GLOP.xlsx
+++ b/CATALOGO 2026 GLOP.xlsx
@@ -391,39 +391,71 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:J16"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>2018</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>14.5</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -431,10 +463,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>12</v>
@@ -446,16 +478,16 @@
         <v>14</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>6.45</v>
+        <v>11.75</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>9.2</v>
+        <v>16.75</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>14.5</v>
+        <v>26.5</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -466,10 +498,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>13</v>
@@ -478,16 +510,16 @@
         <v>14</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>11.75</v>
+        <v>16.2</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>16.75</v>
+        <v>23</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>26.5</v>
+        <v>35</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -495,13 +527,13 @@
         <v>10</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>13</v>
@@ -510,16 +542,16 @@
         <v>14</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>23</v>
+        <v>34.9</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>35</v>
+        <v>54.5</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -527,10 +559,10 @@
         <v>10</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>12</v>
@@ -542,65 +574,62 @@
         <v>14</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>24.5</v>
+        <v>48</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>34.9</v>
+        <v>68.5</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>54.5</v>
+        <v>105.5</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>2014</v>
+        <v>2025</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>48</v>
+        <v>6.4</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>105.5</v>
+        <v>8.54</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>24</v>
+      <c r="B8" s="0" t="s">
+        <v>28</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F8" s="0" t="s">
         <v>26</v>
@@ -612,7 +641,7 @@
         <v>8.54</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -620,16 +649,16 @@
         <v>23</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F9" s="0" t="s">
         <v>26</v>
@@ -641,7 +670,7 @@
         <v>8.54</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -649,16 +678,16 @@
         <v>23</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>2023</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>26</v>
@@ -670,7 +699,7 @@
         <v>8.54</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -678,13 +707,13 @@
         <v>23</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>29</v>
@@ -693,13 +722,13 @@
         <v>26</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>6.4</v>
+        <v>9.5</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>8.54</v>
+        <v>12.67</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -707,13 +736,13 @@
         <v>23</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C12" s="0" t="n">
         <v>2021</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>29</v>
@@ -722,42 +751,45 @@
         <v>26</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>9.5</v>
+        <v>19.57</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>12.67</v>
+        <v>26.11</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>26.11</v>
-      </c>
       <c r="J13" s="0" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -765,31 +797,31 @@
         <v>39</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>16.2</v>
+        <v>13.37</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -797,13 +829,13 @@
         <v>39</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>42</v>
@@ -812,47 +844,15 @@
         <v>47</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>13.37</v>
+        <v>9.7</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>9.7</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="J16" s="0" t="s">
         <v>51</v>
       </c>
     </row>

--- a/CATALOGO 2026 GLOP.xlsx
+++ b/CATALOGO 2026 GLOP.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="81">
   <si>
     <t xml:space="preserve">BODEGA</t>
   </si>
@@ -176,6 +176,93 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.lareservedusommelier.com/wp-content/uploads/2025/04/vin-aure-la-reserve-du-sommelier-vianney-danen-aix-en-provence-transparent-scaled.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERRA I BARCELÓ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUCALÀ NEGRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERRA ALTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://i0.wp.com/jswineworld.com/wp-content/uploads/2022/09/aucala-red-2020.jpg?resize=352%2C1024&amp;ssl=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUCALÀ BLANC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARNACHA BLANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bodeboca.com/sites/default/files/styles/mainbottle_normal/public/wines/2024-10/bot-aucala-blanco-2023.png?itok=Zil6UFtB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOLET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA FADA DE LES VINYES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARNACHA BLANCA, FORCADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENEDÉS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/219-thickbox_default/bolet-vino-la-fada-de-les-vinyes-eco-do-penedes.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VINYA SOTA BOSC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSCATEL, GEWÜRZTRAMINER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/231-thickbox_default/bolet-vi-vinya-sota-bosc-25-eco-penedes.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMAGROC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XARELLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/227-large_default/bolet-vi-camagroc-xarello-25-eco-penedes.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APAGALLUMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINOT NOIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/218-large_default/bolet-vi-apagallums-24-eco-do-penedes.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANTARELUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULL DE LLEBRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/170-thickbox_default/vino-bolet-cantarelus-ull-de-llebre-21-eco-penedes.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARNACHA, FORCADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/235-thickbox_default/bolet-vino-la-fada-de-les-vinyes-biodinamico.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREDOLIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERNET SAUVIGNON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/167-thickbox_default/vino-bolet-fredolic-21-natural-sin-sulfitos-ecologico.jpg</t>
   </si>
 </sst>
 </file>
@@ -391,71 +478,39 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A2:J25"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>9</v>
-      </c>
-    </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>2018</v>
+        <v>1</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>2</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>9.2</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>14.5</v>
+        <v>5</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>8</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -463,10 +518,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>12</v>
@@ -478,16 +533,16 @@
         <v>14</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>11.75</v>
+        <v>6.45</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>16.75</v>
+        <v>9.2</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>26.5</v>
+        <v>14.5</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -498,10 +553,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>13</v>
@@ -510,16 +565,16 @@
         <v>14</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>16.2</v>
+        <v>11.75</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>23</v>
+        <v>16.75</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>35</v>
+        <v>26.5</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -527,13 +582,13 @@
         <v>10</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>13</v>
@@ -542,16 +597,16 @@
         <v>14</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>24.5</v>
+        <v>16.2</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>34.9</v>
+        <v>23</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>54.5</v>
+        <v>35</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -559,10 +614,10 @@
         <v>10</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>12</v>
@@ -574,62 +629,65 @@
         <v>14</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>48</v>
+        <v>24.5</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>68.5</v>
+        <v>34.9</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>105.5</v>
+        <v>54.5</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>21</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>6.4</v>
+        <v>48</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>8.54</v>
+        <v>68.5</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>105.5</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>28</v>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F8" s="0" t="s">
         <v>26</v>
@@ -641,7 +699,7 @@
         <v>8.54</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -649,16 +707,16 @@
         <v>23</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F9" s="0" t="s">
         <v>26</v>
@@ -670,7 +728,7 @@
         <v>8.54</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -678,16 +736,16 @@
         <v>23</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>2023</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>26</v>
@@ -699,7 +757,7 @@
         <v>8.54</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -707,13 +765,13 @@
         <v>23</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>29</v>
@@ -722,13 +780,13 @@
         <v>26</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>12.67</v>
+        <v>8.54</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -736,13 +794,13 @@
         <v>23</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" s="0" t="n">
         <v>2021</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>29</v>
@@ -751,45 +809,42 @@
         <v>26</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>19.57</v>
+        <v>9.5</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>26.11</v>
+        <v>12.67</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>12</v>
+        <v>19.57</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>23</v>
+        <v>26.11</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -797,31 +852,31 @@
         <v>39</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>9.9</v>
+        <v>12</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>13.37</v>
+        <v>16.2</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -829,13 +884,13 @@
         <v>39</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>42</v>
@@ -844,16 +899,330 @@
         <v>47</v>
       </c>
       <c r="G15" s="1" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>7.2</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H16" s="1" t="n">
         <v>9.7</v>
       </c>
-      <c r="I15" s="1" t="n">
+      <c r="I16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="J15" s="0" t="s">
+      <c r="J16" s="0" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="J17" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="J18" s="0" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="J19" s="0" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J20" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J21" s="0" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J23" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="J24" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J25" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/CATALOGO 2026 GLOP.xlsx
+++ b/CATALOGO 2026 GLOP.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="135">
   <si>
     <t xml:space="preserve">BODEGA</t>
   </si>
@@ -229,7 +229,7 @@
     <t xml:space="preserve">XARELLO</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.cavasbolet.com/227-large_default/bolet-vi-camagroc-xarello-25-eco-penedes.jpg</t>
+    <t xml:space="preserve">https://www.cavasbolet.com/227-thickbox_default/bolet-vi-camagroc-xarello-25-eco-penedes.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">APAGALLUMS</t>
@@ -238,7 +238,7 @@
     <t xml:space="preserve">PINOT NOIR</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.cavasbolet.com/218-large_default/bolet-vi-apagallums-24-eco-do-penedes.jpg</t>
+    <t xml:space="preserve">https://www.cavasbolet.com/218-thickbox_default/bolet-vi-apagallums-24-eco-do-penedes.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">CANTARELUS</t>
@@ -263,6 +263,168 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.cavasbolet.com/167-thickbox_default/vino-bolet-fredolic-21-natural-sin-sulfitos-ecologico.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVA BRUT CLASSIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACABEO, XARELLO, PARELLADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/133-thickbox_default/cava-bolet-brut-classic-ecologico.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVA BRUT RESERVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XARELLO, MACABEO, PARELLADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/192-thickbox_default/cava-bolet-brut-reserva-eco.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVA BRUT ROSAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/189-thickbox_default/cava-bolet-rosat-pinot-noir-brut-reserva-eco.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVA BRUT NATURE RESERVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/137-thickbox_default/cava-bolet-brut-nature-reserva-eco.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVA GRAN RESERVA 1911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/190-thickbox_default/cava-bolet-gran-reserva-brut-1911-eco.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVA GRAN RESERVA CARTOIXÀ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cavasbolet.com/136-thickbox_default/cava-bolet-cartoixa-gran-reserva-eco.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORRE DEL VEGUER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECLECTIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAB.SAUVIGNON, SYRAH, GARNACHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2019/06/ECLECTIC-2016.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABELLEROL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSCATEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2023/08/abellerol.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FONOLL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XARELLO, XARELLO ROJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2023/08/fonoll.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARICEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALVASIA DE SITGES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2019/06/maricel-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JERONIMUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2023/08/jeronimus.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2023/08/pur-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARTA BRUT NATURE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2023/08/marta.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAÏMS INMORTALITAT BLANC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2019/06/raims-immortalitat-blanc.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAÏMS INMORTALITAT TINTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAB.SAUVIGNON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2023/08/raims16.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLUM DEL CADÍ TINTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERDANYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2023/08/llum-cadi-negre.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLUM DEL CADÍ BLANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIESLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2023/08/llum-cadi-blanc.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL CUCUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCA DE BARBERÀ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2023/08/el-cucut.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA ROSADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2023/08/la-rosada.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINDICAT DEL PRIORAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARNACHA, SYRAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIORAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2026/04/sindicat-2-1.png</t>
   </si>
 </sst>
 </file>
@@ -344,7 +506,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -358,6 +520,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -484,7 +650,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1229,6 +1395,598 @@
       </c>
       <c r="J24" s="1" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>9.8</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J31" s="0" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J32" s="0" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="J33" s="0" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="J34" s="0" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="J35" s="0" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="J36" s="0" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="J37" s="0" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J38" s="0" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J39" s="0" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="J40" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="J41" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>9.05</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J42" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="J43" s="0" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="J44" s="0" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/CATALOGO 2026 GLOP.xlsx
+++ b/CATALOGO 2026 GLOP.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="187">
   <si>
     <t xml:space="preserve">BODEGA</t>
   </si>
@@ -425,6 +425,162 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2026/04/sindicat-2-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERRE DI RAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARDONNAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I.G.T.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TREVENEZIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://terredirai.it/storage/2024/07/chardonnay-terre-di-rai-700x1049.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINOT GRIGIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://terredirai.it/storage/2024/07/pinot-grigio-terre-di-rai-700x1049.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBOLLA GIALLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://terredirai.it/storage/2024/07/ricolla-gialla-terre-di-rai-700x1049.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAUVIGNON BLANC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://terredirai.it/storage/2024/07/sauvignon-blanc-terre-di-rai-700x1049.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLUSH PINOT GRIGIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://terredirai.it/storage/2024/07/pinot-grigio-blush-terre-di-rai-700x1049.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERLOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://terredirai.it/storage/2024/07/merlot-terre-di-rai-700x1049.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://terredirai.it/storage/2024/06/sauvignon-terre-di-rai-700x1049.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDMUND MACH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEWÜRZTRAMINER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D.O.C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRENTINO ALTO ADIGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fmach.it/var/homepagefmach/storage/images/media/images/gewuerztraminer-trentino-doc_popup2/91256-1-ita-IT/Gewuerztraminer-Trentino-DOC_popup_medium.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fmach.it/var/homepagefmach/storage/images/media/images/riesling-trentino-doc_popup2/91082-1-ita-IT/Riesling-Trentino-DOC_popup_medium.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fmach.it/var/homepagefmach/storage/images/media/images/pinot-grigio-trentino-doc_popup4/161790-1-ita-IT/Pinot-Grigio-Trentino-DOC_popup_medium.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAGREIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fmach.it/var/homepagefmach/storage/images/media/images/lagrein-trentino-doc_popup2/91541-1-ita-IT/Lagrein-Trentino-DOC_popup_medium.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA RAIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISERVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORTESE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D.O.C.G.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAVI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://la-raia.it/wp-content/uploads/2025/08/gaviriserva-new-1024x1024.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PISÉ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://la-raia.it/wp-content/uploads/2025/08/pisenew-1024x1024.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://la-raia.it/wp-content/uploads/2025/01/i-vini-1024x1024.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MÜLLER THURGAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.meranerweinhaus.com/media/image/c3/6f/20/Mueller-Thrugau_Festival_Flaschenfoto_aktualisiert_600x600@2x.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAUVIGNON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.meranerweinhaus.com/media/image/81/7e/56/Chardonnay_Festival_Burggraefler_web_600x600@2x.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WEISSBURGUNDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINOT BLANC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.meranerweinhaus.com/media/image/c3/09/8d/Weissburgunder_Festival_Flaschenfoto_web_600x600@2x.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLAUBURGUNDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.meranerweinhaus.com/media/image/a8/15/05/blauburgunder-festival_600x600@2x.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPUMANTE BRUT RISERVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARDONNAY, PINOT BLANC, PINOT NOIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.meranerweinhaus.com/media/image/6f/d4/d0/sekt-brut-36_600x600@2x.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEVOLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHIANTI CLASSICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANGIOVESE, CANAIOLO, COLORINO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://store.dwineclub.it/pub/media/catalog/product/cache/small_image/400x400/beff4985b56e3afdbeabfc89641a4582/d/i/dievole-chianti-classico_5_1_1.jpg</t>
   </si>
 </sst>
 </file>
@@ -650,7 +806,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1590,403 +1746,1007 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="0" t="s">
+      <c r="E31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="2" t="n">
         <v>10.55</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I31" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="J31" s="0" t="s">
+      <c r="J31" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="0" t="s">
+      <c r="E32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="2" t="n">
         <v>7.75</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I32" s="2" t="n">
         <v>12.5</v>
       </c>
-      <c r="J32" s="0" t="s">
+      <c r="J32" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="0" t="s">
+      <c r="E33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="2" t="n">
         <v>9.2</v>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="I33" s="2" t="n">
         <v>14.75</v>
       </c>
-      <c r="J33" s="0" t="s">
+      <c r="J33" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="0" t="n">
+      <c r="C34" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="0" t="s">
+      <c r="E34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="2" t="n">
         <v>11.25</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="I34" s="2" t="n">
         <v>18.25</v>
       </c>
-      <c r="J34" s="0" t="s">
+      <c r="J34" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="0" t="s">
+      <c r="E35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I35" s="2" t="n">
         <v>25.75</v>
       </c>
-      <c r="J35" s="0" t="s">
+      <c r="J35" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E36" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="0" t="s">
+      <c r="E36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="I36" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="J36" s="0" t="s">
+      <c r="J36" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="0" t="n">
+      <c r="C37" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E37" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="0" t="s">
+      <c r="E37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="2" t="n">
         <v>17.75</v>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I37" s="2" t="n">
         <v>28.5</v>
       </c>
-      <c r="J37" s="0" t="s">
+      <c r="J37" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E38" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="0" t="s">
+      <c r="E38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="I38" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="J38" s="0" t="s">
+      <c r="J38" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C39" s="0" t="n">
+      <c r="C39" s="1" t="n">
         <v>2017</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E39" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="0" t="s">
+      <c r="E39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="I39" s="2" t="n">
         <v>30.5</v>
       </c>
-      <c r="J39" s="0" t="s">
+      <c r="J39" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="0" t="n">
+      <c r="C40" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="2" t="n">
         <v>24.25</v>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="I40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="J40" s="0" t="s">
+      <c r="J40" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="0" t="n">
+      <c r="C41" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="I41" s="2" t="n">
         <v>30.75</v>
       </c>
-      <c r="J41" s="0" t="s">
+      <c r="J41" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="0" t="n">
+      <c r="C42" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E42" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="0" t="s">
+      <c r="E42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="2" t="n">
         <v>9.05</v>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="I42" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="J42" s="0" t="s">
+      <c r="J42" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C43" s="0" t="n">
+      <c r="C43" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E43" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="0" t="s">
+      <c r="E43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="2" t="n">
         <v>7.9</v>
       </c>
-      <c r="I43" s="4" t="n">
+      <c r="I43" s="2" t="n">
         <v>12.75</v>
       </c>
-      <c r="J43" s="0" t="s">
+      <c r="J43" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C44" s="0" t="n">
+      <c r="C44" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="E44" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="2" t="n">
         <v>26.25</v>
       </c>
-      <c r="I44" s="4" t="n">
+      <c r="I44" s="2" t="n">
         <v>42.25</v>
       </c>
-      <c r="J44" s="0" t="s">
+      <c r="J44" s="1" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>9.45</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>8.62</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>8.11</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="C56" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="J56" s="0" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="F57" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="J57" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>8.36</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="J58" s="0" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="C59" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="F59" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>8.28</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J59" s="0" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="E60" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="F60" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>9.12</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J60" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="E61" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="F61" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>8.28</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J61" s="0" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E62" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="F62" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J62" s="0" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="F63" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="J63" s="0" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="E64" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="F64" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J64" s="0" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/CATALOGO 2026 GLOP.xlsx
+++ b/CATALOGO 2026 GLOP.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="261">
   <si>
     <t xml:space="preserve">BODEGA</t>
   </si>
@@ -484,6 +484,33 @@
     <t xml:space="preserve">https://www.lareservedusommelier.com/wp-content/uploads/2025/04/vin-aure-la-reserve-du-sommelier-vianney-danen-aix-en-provence-transparent-scaled.png</t>
   </si>
   <si>
+    <t xml:space="preserve">LAS VIRTUDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARROCERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSCATEL, SAUVIGNON BLANC, MACABEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bodegavirtudes.com/wp-content/uploads/2021/04/arrocero-blanco.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESENCIA DEL MEDITERRANEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSCATEL, SAUVIGNON BLANC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bodegavirtudes.com/wp-content/uploads/2021/09/esencia-del-mediterraneo.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TESORO DE VILLENA FONDILLON SOLERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bodegavirtudes.com/wp-content/uploads/2021/03/img-producto-fondillon-1.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">MERAN</t>
   </si>
   <si>
@@ -523,6 +550,21 @@
     <t xml:space="preserve">https://www.meranerweinhaus.com/media/image/6f/d4/d0/sekt-brut-36_600x600@2x.webp</t>
   </si>
   <si>
+    <t xml:space="preserve">OLIMARUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIMARUM VIÑEDOS DE ALTURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://olimarum.com/wp-content/uploads/2025/06/OLIMARUM-21_2.web_.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUERCUS PYRENAICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://olimarum.com/wp-content/uploads/2025/06/QUERCUS-2.web_.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">SERRA I BARCELÓ</t>
   </si>
   <si>
@@ -692,6 +734,75 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.torredelveguer.com/wp-content/uploads/2026/04/sindicat-2-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALE BENFEITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REI ARTUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALICANTE BOUSCHET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.V.R.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LISBOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grandesescolhas.com/wp-content/uploads/2026/03/V19648.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MASSIMO SYRAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://quintavalebenfeito.pt/wp-content/uploads/2023/12/20-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MASSIMO TOURIGA NACIONAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOURIGA NACIONAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://prime-wine.pt/wp-content/uploads/2025/03/PW_0000_Qta-Vale-Benfeito-Touriga-Nacional.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOTA ARINTO RESERVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARINTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://quintavalebenfeito.pt/wp-content/uploads/2024/02/Carlota-a-Imperatriz-Arinto-Reserva-2020.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOTA MOSCATEL GALEGO BRANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSCATEL GALEGO BRANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://quintavalebenfeito.pt/wp-content/uploads/2021/11/Vinho-Branco-Carlota-a-Imperatriz-2020-Moscatel-Galego_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOTA FERNÂO PIRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNÂO PIRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://quintavalebenfeito.pt/wp-content/uploads/2021/11/Carlota-a-Imperatriz-2021-Fernao-Pires.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALADOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://quintavalebenfeito.pt/wp-content/uploads/2021/11/Vinho-Rose-Leonor-a-Princesa_final.png</t>
   </si>
 </sst>
 </file>
@@ -926,7 +1037,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2468,110 +2579,113 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="0" t="n">
         <v>2025</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>8.28</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J50" s="1" t="s">
+      <c r="D50" s="0" t="s">
         <v>156</v>
       </c>
+      <c r="E50" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="J50" s="0" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C51" s="1" t="n">
+      <c r="B51" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" s="0" t="n">
         <v>2025</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>9.12</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>158</v>
+      <c r="D51" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J51" s="0" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C52" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>8.28</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="J52" s="1" t="s">
+      <c r="B52" s="0" t="s">
         <v>161</v>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>1972</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="J52" s="0" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>12</v>
@@ -2580,30 +2694,30 @@
         <v>98</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>10.07</v>
+        <v>8.28</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>13.59</v>
+        <v>11.17</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.9</v>
+        <v>11.7</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>12</v>
@@ -2612,42 +2726,42 @@
         <v>98</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>18.62</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>25.13</v>
+        <v>9.12</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>28.65</v>
+        <v>11.7</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>168</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>6.18</v>
+        <v>8.28</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>7.85</v>
+        <v>11.17</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>14.2</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>170</v>
@@ -2655,234 +2769,246 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>171</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="E57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C57" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F57" s="1" t="s">
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
         <v>176</v>
       </c>
-      <c r="G57" s="2" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="J57" s="1" t="s">
+      <c r="B58" s="0" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F58" s="1" t="s">
+      <c r="C58" s="0" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="J58" s="0" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
         <v>176</v>
       </c>
-      <c r="G58" s="2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="C59" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="J59" s="1" t="s">
+      <c r="C59" s="0" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F59" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="J59" s="0" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>108</v>
+        <v>182</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>4.18</v>
+        <v>6.18</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>5.64</v>
+        <v>7.85</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C61" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>102</v>
+        <v>186</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>3.96</v>
+        <v>6.36</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>5.35</v>
+        <v>7.85</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>3.6</v>
+        <v>3.93</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>4.86</v>
+        <v>5.31</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2890,28 +3016,28 @@
         <v>188</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D64" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>29</v>
+      <c r="G64" s="2" t="n">
+        <v>4.34</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>17</v>
+        <v>5.86</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2919,28 +3045,28 @@
         <v>188</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>29</v>
+        <v>190</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>4.18</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>12.5</v>
+        <v>5.64</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2948,28 +3074,28 @@
         <v>188</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C66" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>195</v>
+        <v>102</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>29</v>
+        <v>190</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>3.96</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>9.2</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>14.75</v>
+        <v>5.35</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2977,25 +3103,25 @@
         <v>188</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>198</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>29</v>
+        <v>190</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>3.6</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>18.25</v>
+        <v>4.86</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>199</v>
@@ -3006,25 +3132,25 @@
         <v>188</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C68" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="E68" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>29</v>
+        <v>190</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>3.63</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>25.75</v>
+        <v>4.86</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>201</v>
@@ -3032,16 +3158,16 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>28</v>
@@ -3050,24 +3176,24 @@
         <v>29</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>14.5</v>
+        <v>10.55</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23.5</v>
+        <v>17</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>119</v>
@@ -3079,27 +3205,27 @@
         <v>29</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>17.75</v>
+        <v>7.75</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>28.5</v>
+        <v>12.5</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>28</v>
@@ -3108,27 +3234,27 @@
         <v>29</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>18</v>
+        <v>9.2</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>29</v>
+        <v>14.75</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>28</v>
@@ -3137,152 +3263,518 @@
         <v>29</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>19</v>
+        <v>11.25</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>30.5</v>
+        <v>18.25</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>211</v>
+        <v>29</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>24.25</v>
+        <v>16</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>39</v>
+        <v>25.75</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>100</v>
+        <v>212</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>211</v>
+        <v>29</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>30.75</v>
+        <v>23.5</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>216</v>
+        <v>29</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>9.05</v>
+        <v>17.75</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>14.5</v>
+        <v>28.5</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>216</v>
+        <v>29</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>7.9</v>
+        <v>18</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>12.75</v>
+        <v>29</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>222</v>
+        <v>29</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>26.25</v>
+        <v>19</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>42.25</v>
+        <v>30.5</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>223</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>9.05</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="C83" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="F83" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J83" s="0" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="C84" s="0" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D84" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="E84" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="F84" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J84" s="0" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="C85" s="0" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="F85" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="J85" s="0" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="C86" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="F86" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="J86" s="0" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="C87" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D87" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="F87" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J87" s="0" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="C88" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D88" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="E88" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="F88" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J88" s="0" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C89" s="0" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E89" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="F89" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I89" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J89" s="0" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/CATALOGO 2026 GLOP.xlsx
+++ b/CATALOGO 2026 GLOP.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="308">
   <si>
     <t xml:space="preserve">BODEGA</t>
   </si>
@@ -803,6 +803,147 @@
   </si>
   <si>
     <t xml:space="preserve">https://quintavalebenfeito.pt/wp-content/uploads/2021/11/Vinho-Rose-Leonor-a-Princesa_final.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIRIBALDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILANDOLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARNEIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANGHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2018/12/Langhe-Arneis-Giribaldi.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSCATO D’ASTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSCATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.mrvinos.com/data/vinos/53169/mario-giribaldi-moscato-dasti-1770809_e.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJ SUPERIORE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARBERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARBERA D’ALBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2018/12/Barbera-dAlba-Caj-Giribaldi.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPO DEI FICHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2018/12/Riesling_Giribaldi_2024_r.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I RISI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.houseoftownend.com/Content/Images/Products/GAVI010.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARBERA D’ASTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tse4.mm.bing.net/th/id/OIP.FkZBh5W_Kpz-k5E7rYf9twAAAA?rs=1&amp;pid=ImgDetMain&amp;o=7&amp;rm=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALUPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOLCETTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOLCETTO D’ALBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2018/12/Dolcetto-Calupo-Giribaldi.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCA D’ORO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEBBIOLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEBBIOLO D’ALBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2018/12/Nebbiolo-Conca-dOro-Giribaldi.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPO DELPESCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEBBIOLO LANGHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2019/08/Nebbiolo-Campo-del-pesco-Giribaldi.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANGHE ROSSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEBBIOLO, BARBERA, DOLCETTO, PINOT NOIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://agilewines.ca/assets/uploads/w87/Langhe_Rosso_Azienda_Giribaldi_bio_Organic.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARBARESCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2018/12/Barbaresco-2022-Giribaldi.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAROLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2020/12/Barolo-2021-Giribaldi_r.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIGNA RAVERA RISERVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2018/12/Barolo-Ravera_2016_r.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAS DOSÈ RISERVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINOT NOIR, CHARDONNAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTA LANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2025/05/alta-langa-2015-pas-dose-riserva-Black-1.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXTRA BRUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2018/12/Alta-langa-2018_r.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAS DOSÈ ROSÈ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2025/05/alta-langa-2021-Rose-1.jpg</t>
   </si>
 </sst>
 </file>
@@ -914,15 +1055,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1037,7 +1169,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2108,226 +2240,226 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="E35" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="2" t="n">
         <v>5.7</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="2" t="n">
         <v>7.7</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I35" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J35" s="0" t="s">
+      <c r="J35" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="2" t="n">
         <v>5.7</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="2" t="n">
         <v>7.7</v>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="I36" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J36" s="0" t="s">
+      <c r="J36" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="0" t="n">
+      <c r="C37" s="1" t="n">
         <v>2008</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="2" t="n">
         <v>12.9</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I37" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="J37" s="0" t="s">
+      <c r="J37" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E38" s="0" t="s">
+      <c r="E38" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="2" t="n">
         <v>7.5</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="2" t="n">
         <v>10.1</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="I38" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="J38" s="0" t="s">
+      <c r="J38" s="1" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="0" t="n">
+      <c r="C39" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="2" t="n">
         <v>5.95</v>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="I39" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="J39" s="0" t="s">
+      <c r="J39" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="0" t="n">
+      <c r="C40" s="1" t="n">
         <v>1988</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E40" s="0" t="s">
+      <c r="E40" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="I40" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="J40" s="0" t="s">
+      <c r="J40" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="0" t="n">
+      <c r="C41" s="1" t="n">
         <v>1972</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="E41" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="2" t="n">
         <v>370</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="I41" s="2" t="n">
         <v>372</v>
       </c>
-      <c r="J41" s="0" t="s">
+      <c r="J41" s="1" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2579,98 +2711,98 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C50" s="0" t="n">
+      <c r="C50" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="D50" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E50" s="0" t="s">
+      <c r="E50" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="2" t="n">
         <v>1.8</v>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="H50" s="2" t="n">
         <v>2.45</v>
       </c>
-      <c r="I50" s="4" t="n">
+      <c r="I50" s="2" t="n">
         <v>4.45</v>
       </c>
-      <c r="J50" s="0" t="s">
+      <c r="J50" s="1" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C51" s="0" t="n">
+      <c r="C51" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="D51" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E51" s="0" t="s">
+      <c r="E51" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="2" t="n">
         <v>2.6</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="H51" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="I51" s="4" t="n">
+      <c r="I51" s="2" t="n">
         <v>4.8</v>
       </c>
-      <c r="J51" s="0" t="s">
+      <c r="J51" s="1" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C52" s="0" t="n">
+      <c r="C52" s="1" t="n">
         <v>1972</v>
       </c>
-      <c r="D52" s="0" t="s">
+      <c r="D52" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E52" s="0" t="s">
+      <c r="E52" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="2" t="n">
         <v>24.75</v>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="H52" s="2" t="n">
         <v>33.5</v>
       </c>
-      <c r="I52" s="4" t="n">
+      <c r="I52" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="J52" s="0" t="s">
+      <c r="J52" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2832,66 +2964,66 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C58" s="0" t="n">
+      <c r="C58" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="D58" s="0" t="s">
+      <c r="D58" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E58" s="0" t="s">
+      <c r="E58" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="2" t="n">
         <v>6.25</v>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="H58" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="I58" s="4" t="n">
+      <c r="I58" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="J58" s="0" t="s">
+      <c r="J58" s="1" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C59" s="0" t="n">
+      <c r="C59" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E59" s="0" t="s">
+      <c r="E59" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="2" t="n">
         <v>21.25</v>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="H59" s="2" t="n">
         <v>28.7</v>
       </c>
-      <c r="I59" s="4" t="n">
+      <c r="I59" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="J59" s="0" t="s">
+      <c r="J59" s="1" t="s">
         <v>180</v>
       </c>
     </row>
@@ -3557,224 +3689,743 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C83" s="0" t="n">
+      <c r="C83" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D83" s="0" t="s">
+      <c r="D83" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E83" s="0" t="s">
+      <c r="E83" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H83" s="4" t="n">
+      <c r="H83" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="I83" s="4" t="n">
+      <c r="I83" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="J83" s="0" t="s">
+      <c r="J83" s="1" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C84" s="0" t="n">
+      <c r="C84" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="D84" s="0" t="s">
+      <c r="D84" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E84" s="0" t="s">
+      <c r="E84" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="2" t="n">
         <v>8.75</v>
       </c>
-      <c r="H84" s="4" t="n">
+      <c r="H84" s="2" t="n">
         <v>11.8</v>
       </c>
-      <c r="I84" s="4" t="n">
+      <c r="I84" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J84" s="0" t="s">
+      <c r="J84" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C85" s="0" t="n">
+      <c r="C85" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D85" s="0" t="s">
+      <c r="D85" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E85" s="0" t="s">
+      <c r="E85" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="F85" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="2" t="n">
         <v>8.75</v>
       </c>
-      <c r="H85" s="4" t="n">
+      <c r="H85" s="2" t="n">
         <v>11.8</v>
       </c>
-      <c r="I85" s="4" t="n">
+      <c r="I85" s="2" t="n">
         <v>13.29</v>
       </c>
-      <c r="J85" s="0" t="s">
+      <c r="J85" s="1" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C86" s="0" t="n">
+      <c r="C86" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D86" s="0" t="s">
+      <c r="D86" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E86" s="0" t="s">
+      <c r="E86" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="H86" s="4" t="n">
+      <c r="H86" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="I86" s="4" t="n">
+      <c r="I86" s="2" t="n">
         <v>16.95</v>
       </c>
-      <c r="J86" s="0" t="s">
+      <c r="J86" s="1" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C87" s="0" t="n">
+      <c r="C87" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D87" s="0" t="s">
+      <c r="D87" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E87" s="0" t="s">
+      <c r="E87" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H87" s="4" t="n">
+      <c r="H87" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="I87" s="4" t="n">
+      <c r="I87" s="2" t="n">
         <v>7.5</v>
       </c>
-      <c r="J87" s="0" t="s">
+      <c r="J87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C88" s="0" t="n">
+      <c r="C88" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D88" s="0" t="s">
+      <c r="D88" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E88" s="0" t="s">
+      <c r="E88" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="2" t="n">
         <v>3.1</v>
       </c>
-      <c r="H88" s="4" t="n">
+      <c r="H88" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="I88" s="4" t="n">
+      <c r="I88" s="2" t="n">
         <v>7.5</v>
       </c>
-      <c r="J88" s="0" t="s">
+      <c r="J88" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C89" s="0" t="n">
+      <c r="C89" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D89" s="0" t="s">
+      <c r="D89" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E89" s="0" t="s">
+      <c r="E89" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H89" s="4" t="n">
+      <c r="H89" s="2" t="n">
         <v>2.9</v>
       </c>
-      <c r="I89" s="4" t="n">
+      <c r="I89" s="2" t="n">
         <v>7.5</v>
       </c>
-      <c r="J89" s="0" t="s">
+      <c r="J89" s="1" t="s">
         <v>260</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="C93" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="E93" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>9.45</v>
+      </c>
+      <c r="J93" s="0" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="C94" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="E94" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F94" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J94" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="C95" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D95" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="E95" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F95" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="J95" s="0" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="C96" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="E96" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="J96" s="0" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="0" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="E97" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="J97" s="0" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="C98" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="E98" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="J98" s="0" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="C99" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="E99" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="J99" s="0" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="C100" s="0" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D100" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="E100" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F100" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="J100" s="0" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="C101" s="0" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D101" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="E101" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F101" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="J101" s="0" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C102" s="0" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F102" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="J102" s="0" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C103" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D103" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="E103" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F103" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H103" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="J103" s="0" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C104" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D104" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="E104" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F104" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="J104" s="0" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="C105" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D105" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="E105" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F105" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H105" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="J105" s="0" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="C106" s="0" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F106" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J106" s="0" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="C107" s="0" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D107" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="E107" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F107" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="J107" s="0" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/CATALOGO 2026 GLOP.xlsx
+++ b/CATALOGO 2026 GLOP.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="351">
   <si>
     <t xml:space="preserve">BODEGA</t>
   </si>
@@ -944,6 +944,135 @@
   </si>
   <si>
     <t xml:space="preserve">https://vinigiribaldi.it/wp-content/uploads/2025/05/alta-langa-2021-Rose-1.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAUSTINO RIVERA ULECIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOVEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMPRANILLO, GARNACHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D.O.Ca.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIOJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://faustinorivero.com/wp-content/uploads/2022/02/rioja-joven-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARQUES DE REINOSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D.O.Ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://inmortalwines.com/wp-content/uploads/2024/10/CTP_00012.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARQUÉS DE LA CONCORDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIOJA SANTIAGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://marquesdelaconcordia.com/wp-content/uploads/2022/04/M.-Concordia-RS-SEGUNDO-AN%CC%83O.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSBORNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIÑA CUMBRERO CRIANZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinopremier.com/media/catalog/product/cache/070e1948fa79794c1092c01c58a07334/1/5/1551479058.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAMILIA MONJE AMESTOY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUBERRI COSECHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMPRANILLO, VIURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.luberri.com/img/bottle-cosecha.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVEAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALACIO QUEMADO VENDIMIA SELECCIONADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARNACHA TINTORERA, SYRAH, TEMPRANILLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIBERA DE GUADIANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vinopremier.com/media/catalog/product/cache/070e1948fa79794c1092c01c58a07334/v/i/vino-tinto-palacio-quemado-vendimia-seleccionada-vinopremier.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAMILIA GIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUAN GIL ET. AMARILLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUMILLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://store.gilfamily.es/media/products/images/big/5_juan-gil-etiqueta-amarilla.jpg?ver=2010801b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUAN GIL ET. PLATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://store.gilfamily.es/media/products/images/big/6_juan-gil-etiqueta-plata.jpg?ver=5f970715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUAN GIL BLANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://store.gilfamily.es/media/products/images/big/1_juan-gil-blanco.jpg?ver=97851783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELONDRADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUINTA APOLONIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERDEJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUEDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://belondrade.com/wp-content/uploads/2018/02/apolonia-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABADIA RETUERTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECCIÓN ESPECIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMPRANILLO, OTRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V.T.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASTILLA Y LEÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abadia-retuerta.com/wp-content/uploads/2025/10/planilla-vino-imagen-destacada-individual-SE21-e1762337288596.png</t>
   </si>
 </sst>
 </file>
@@ -1025,8 +1154,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1044,6 +1177,10 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1169,3263 +1306,3600 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.1"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>7.37</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>9.95</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>7.37</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>9.95</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>7.37</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>9.95</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>7.37</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>9.95</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>7.71</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>4.47</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>6.05</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>3.81</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>5.15</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>3.81</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="3" t="n">
         <v>5.15</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>3.81</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>5.15</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="3" t="n">
         <v>7.71</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="3" t="n">
         <v>7.64</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="3" t="n">
         <v>4.97</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="3" t="n">
         <v>6.7</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="3" t="n">
         <v>9.8</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="3" t="n">
         <v>7.83</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="3" t="n">
         <v>11.89</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G16" s="3" t="n">
         <v>5.27</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="3" t="n">
         <v>7.11</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>2017</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G17" s="3" t="n">
         <v>10.92</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="3" t="n">
         <v>14.75</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I17" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>2015</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G18" s="3" t="n">
         <v>10.67</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G19" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="3" t="n">
         <v>8.54</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G20" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="3" t="n">
         <v>8.54</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G21" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H21" s="3" t="n">
         <v>8.54</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G22" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="3" t="n">
         <v>8.54</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G23" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="H23" s="3" t="n">
         <v>12.67</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G24" s="3" t="n">
         <v>19.57</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="3" t="n">
         <v>26.11</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="3" t="n">
         <v>6.45</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="3" t="n">
         <v>9.2</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="I25" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" s="2" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>2020</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G26" s="3" t="n">
         <v>11.75</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="3" t="n">
         <v>16.75</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I26" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" s="2" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G27" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H27" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="I27" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>2016</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G28" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H28" s="3" t="n">
         <v>34.9</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="I28" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>2014</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G29" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H29" s="3" t="n">
         <v>68.5</v>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="I29" s="3" t="n">
         <v>105.5</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G30" s="3" t="n">
         <v>10.99</v>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="I30" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" s="2" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G31" s="3" t="n">
         <v>9.45</v>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="H31" s="3" t="n">
         <v>12.75</v>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="I31" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G32" s="3" t="n">
         <v>8.62</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H32" s="3" t="n">
         <v>11.63</v>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="I32" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G33" s="3" t="n">
         <v>8.11</v>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H33" s="3" t="n">
         <v>10.95</v>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="I33" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G34" s="3" t="n">
         <v>10.76</v>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="H34" s="3" t="n">
         <v>14.53</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G35" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="H35" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="I35" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="J35" s="2" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G36" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H36" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="I36" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" s="2" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>2008</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G37" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="H37" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="I37" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" s="2" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G38" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="I38" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" s="2" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G39" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H39" s="3" t="n">
         <v>5.95</v>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="I39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" s="2" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>1988</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G40" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H40" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="I40" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J40" s="2" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>1972</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G41" s="3" t="n">
         <v>275</v>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="H41" s="3" t="n">
         <v>370</v>
       </c>
-      <c r="I41" s="2" t="n">
+      <c r="I41" s="3" t="n">
         <v>372</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" s="2" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G42" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" s="3" t="n">
         <v>27.54</v>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="I42" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" s="2" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G43" s="3" t="n">
         <v>10.41</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="H43" s="3" t="n">
         <v>14.05</v>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="I43" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" s="2" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G44" s="3" t="n">
         <v>12.14</v>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H44" s="3" t="n">
         <v>16.39</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="J44" s="2" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G45" s="3" t="n">
         <v>18.79</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H45" s="3" t="n">
         <v>25.35</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="J45" s="2" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G46" s="3" t="n">
         <v>8.36</v>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H46" s="3" t="n">
         <v>11.29</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="J46" s="2" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G47" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="H47" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="I47" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J47" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G48" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="H48" s="3" t="n">
         <v>13.37</v>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="I48" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="J48" s="2" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G49" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="H49" s="3" t="n">
         <v>9.7</v>
       </c>
-      <c r="I49" s="2" t="n">
+      <c r="I49" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="J49" s="2" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G50" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H50" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="I50" s="3" t="n">
         <v>4.45</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="J50" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G51" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="H51" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="I51" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="J51" s="2" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>1972</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G52" s="3" t="n">
         <v>24.75</v>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="H52" s="3" t="n">
         <v>33.5</v>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I52" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="J52" s="1" t="s">
+      <c r="J52" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G53" s="3" t="n">
         <v>8.28</v>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H53" s="3" t="n">
         <v>11.17</v>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="I53" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="J53" s="1" t="s">
+      <c r="J53" s="2" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G54" s="3" t="n">
         <v>9.12</v>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="I54" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J54" s="2" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G55" s="3" t="n">
         <v>8.28</v>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="H55" s="3" t="n">
         <v>11.17</v>
       </c>
-      <c r="I55" s="2" t="n">
+      <c r="I55" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="J55" s="2" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G56" s="3" t="n">
         <v>10.07</v>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H56" s="3" t="n">
         <v>13.59</v>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="I56" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="J56" s="2" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G57" s="3" t="n">
         <v>18.62</v>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="H57" s="3" t="n">
         <v>25.13</v>
       </c>
-      <c r="I57" s="2" t="n">
+      <c r="I57" s="3" t="n">
         <v>28.65</v>
       </c>
-      <c r="J57" s="1" t="s">
+      <c r="J57" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G58" s="3" t="n">
         <v>6.25</v>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="H58" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="I58" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="J58" s="2" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G59" s="3" t="n">
         <v>21.25</v>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H59" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="I59" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="J59" s="2" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G60" s="3" t="n">
         <v>6.18</v>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="H60" s="3" t="n">
         <v>7.85</v>
       </c>
-      <c r="J60" s="1" t="s">
+      <c r="J60" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G61" s="3" t="n">
         <v>6.36</v>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="H61" s="3" t="n">
         <v>7.85</v>
       </c>
-      <c r="J61" s="1" t="s">
+      <c r="J61" s="2" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G62" s="3" t="n">
         <v>3.93</v>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H62" s="3" t="n">
         <v>5.31</v>
       </c>
-      <c r="J62" s="1" t="s">
+      <c r="J62" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G63" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="H63" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J63" s="1" t="s">
+      <c r="J63" s="2" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G64" s="3" t="n">
         <v>4.34</v>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H64" s="3" t="n">
         <v>5.86</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="J64" s="2" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G65" s="3" t="n">
         <v>4.18</v>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="H65" s="3" t="n">
         <v>5.64</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="J65" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G66" s="3" t="n">
         <v>3.96</v>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="H66" s="3" t="n">
         <v>5.35</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="J66" s="2" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G67" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="H67" s="3" t="n">
         <v>4.86</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="J67" s="2" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G68" s="3" t="n">
         <v>3.63</v>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="H68" s="3" t="n">
         <v>4.86</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="J68" s="2" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H69" s="2" t="n">
+      <c r="H69" s="3" t="n">
         <v>10.55</v>
       </c>
-      <c r="I69" s="2" t="n">
+      <c r="I69" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="J69" s="2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H70" s="2" t="n">
+      <c r="H70" s="3" t="n">
         <v>7.75</v>
       </c>
-      <c r="I70" s="2" t="n">
+      <c r="I70" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="J70" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="H71" s="3" t="n">
         <v>9.2</v>
       </c>
-      <c r="I71" s="2" t="n">
+      <c r="I71" s="3" t="n">
         <v>14.75</v>
       </c>
-      <c r="J71" s="1" t="s">
+      <c r="J71" s="2" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E72" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="H72" s="3" t="n">
         <v>11.25</v>
       </c>
-      <c r="I72" s="2" t="n">
+      <c r="I72" s="3" t="n">
         <v>18.25</v>
       </c>
-      <c r="J72" s="1" t="s">
+      <c r="J72" s="2" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H73" s="2" t="n">
+      <c r="H73" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="I73" s="2" t="n">
+      <c r="I73" s="3" t="n">
         <v>25.75</v>
       </c>
-      <c r="J73" s="1" t="s">
+      <c r="J73" s="2" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E74" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H74" s="2" t="n">
+      <c r="H74" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="I74" s="2" t="n">
+      <c r="I74" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="J74" s="1" t="s">
+      <c r="J74" s="2" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H75" s="2" t="n">
+      <c r="H75" s="3" t="n">
         <v>17.75</v>
       </c>
-      <c r="I75" s="2" t="n">
+      <c r="I75" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="J75" s="1" t="s">
+      <c r="J75" s="2" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C76" s="1" t="n">
+      <c r="C76" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H76" s="2" t="n">
+      <c r="H76" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="I76" s="2" t="n">
+      <c r="I76" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="J76" s="2" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C77" s="1" t="n">
+      <c r="C77" s="2" t="n">
         <v>2017</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H77" s="2" t="n">
+      <c r="H77" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="I77" s="2" t="n">
+      <c r="I77" s="3" t="n">
         <v>30.5</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="J77" s="2" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C78" s="1" t="n">
+      <c r="C78" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H78" s="3" t="n">
         <v>24.25</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="I78" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="J78" s="1" t="s">
+      <c r="J78" s="2" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C79" s="1" t="n">
+      <c r="C79" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D79" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F79" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="H79" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="I79" s="2" t="n">
+      <c r="I79" s="3" t="n">
         <v>30.75</v>
       </c>
-      <c r="J79" s="1" t="s">
+      <c r="J79" s="2" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C80" s="1" t="n">
+      <c r="C80" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E80" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="H80" s="3" t="n">
         <v>9.05</v>
       </c>
-      <c r="I80" s="2" t="n">
+      <c r="I80" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="J80" s="1" t="s">
+      <c r="J80" s="2" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C81" s="1" t="n">
+      <c r="C81" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H81" s="2" t="n">
+      <c r="H81" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="I81" s="2" t="n">
+      <c r="I81" s="3" t="n">
         <v>12.75</v>
       </c>
-      <c r="J81" s="1" t="s">
+      <c r="J81" s="2" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C82" s="1" t="n">
+      <c r="C82" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E82" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F82" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H82" s="3" t="n">
         <v>26.25</v>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="I82" s="3" t="n">
         <v>42.25</v>
       </c>
-      <c r="J82" s="1" t="s">
+      <c r="J82" s="2" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C83" s="1" t="n">
+      <c r="C83" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F83" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="G83" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H83" s="2" t="n">
+      <c r="H83" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="I83" s="2" t="n">
+      <c r="I83" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="J83" s="1" t="s">
+      <c r="J83" s="2" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C84" s="1" t="n">
+      <c r="C84" s="2" t="n">
         <v>2020</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D84" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E84" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F84" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="G84" s="3" t="n">
         <v>8.75</v>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="H84" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I84" s="2" t="n">
+      <c r="I84" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="J84" s="1" t="s">
+      <c r="J84" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C85" s="1" t="n">
+      <c r="C85" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E85" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F85" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="G85" s="3" t="n">
         <v>8.75</v>
       </c>
-      <c r="H85" s="2" t="n">
+      <c r="H85" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I85" s="2" t="n">
+      <c r="I85" s="3" t="n">
         <v>13.29</v>
       </c>
-      <c r="J85" s="1" t="s">
+      <c r="J85" s="2" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C86" s="1" t="n">
+      <c r="C86" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E86" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F86" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="H86" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="I86" s="2" t="n">
+      <c r="I86" s="3" t="n">
         <v>16.95</v>
       </c>
-      <c r="J86" s="1" t="s">
+      <c r="J86" s="2" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C87" s="1" t="n">
+      <c r="C87" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D87" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E87" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F87" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="G87" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="H87" s="2" t="n">
+      <c r="H87" s="3" t="n">
         <v>4.75</v>
       </c>
-      <c r="I87" s="2" t="n">
+      <c r="I87" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="J87" s="1" t="s">
+      <c r="J87" s="2" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C88" s="1" t="n">
+      <c r="C88" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E88" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F88" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="G88" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="H88" s="2" t="n">
+      <c r="H88" s="3" t="n">
         <v>4.75</v>
       </c>
-      <c r="I88" s="2" t="n">
+      <c r="I88" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="J88" s="1" t="s">
+      <c r="J88" s="2" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C89" s="1" t="n">
+      <c r="C89" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E89" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F89" s="1" t="s">
+      <c r="F89" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="G89" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="H89" s="2" t="n">
+      <c r="H89" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="I89" s="2" t="n">
+      <c r="I89" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="J89" s="1" t="s">
+      <c r="J89" s="2" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C90" s="1" t="n">
+      <c r="C90" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E90" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="F90" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="G90" s="2" t="n">
+      <c r="G90" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="H90" s="3" t="n">
         <v>9.35</v>
       </c>
-      <c r="J90" s="1" t="s">
+      <c r="J90" s="2" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C91" s="1" t="n">
+      <c r="C91" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E91" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F91" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="G91" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="H91" s="2" t="n">
+      <c r="H91" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="J91" s="1" t="s">
+      <c r="J91" s="2" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C92" s="1" t="n">
+      <c r="C92" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E92" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="F92" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="G92" s="2" t="n">
+      <c r="G92" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="H92" s="2" t="n">
+      <c r="H92" s="3" t="n">
         <v>9.75</v>
       </c>
-      <c r="J92" s="1" t="s">
+      <c r="J92" s="2" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C93" s="0" t="n">
+      <c r="C93" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D93" s="0" t="s">
+      <c r="D93" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E93" s="0" t="s">
+      <c r="E93" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H93" s="4" t="n">
+      <c r="H93" s="3" t="n">
         <v>9.45</v>
       </c>
-      <c r="J93" s="0" t="s">
+      <c r="J93" s="2" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C94" s="0" t="n">
+      <c r="C94" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="D94" s="0" t="s">
+      <c r="D94" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E94" s="0" t="s">
+      <c r="E94" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="3" t="n">
         <v>7.3</v>
       </c>
-      <c r="H94" s="4" t="n">
+      <c r="H94" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="J94" s="0" t="s">
+      <c r="J94" s="2" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C95" s="0" t="n">
+      <c r="C95" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="D95" s="0" t="s">
+      <c r="D95" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E95" s="0" t="s">
+      <c r="E95" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="H95" s="4" t="n">
+      <c r="H95" s="3" t="n">
         <v>10.15</v>
       </c>
-      <c r="J95" s="0" t="s">
+      <c r="J95" s="2" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C96" s="0" t="n">
+      <c r="C96" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D96" s="0" t="s">
+      <c r="D96" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E96" s="0" t="s">
+      <c r="E96" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="F96" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="H96" s="4" t="n">
+      <c r="H96" s="3" t="n">
         <v>7.45</v>
       </c>
-      <c r="J96" s="0" t="s">
+      <c r="J96" s="2" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="B97" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C97" s="0" t="n">
+      <c r="C97" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D97" s="0" t="s">
+      <c r="D97" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E97" s="0" t="s">
+      <c r="E97" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="F97" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="H97" s="4" t="n">
+      <c r="H97" s="3" t="n">
         <v>13.35</v>
       </c>
-      <c r="J97" s="0" t="s">
+      <c r="J97" s="2" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="B98" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C98" s="0" t="n">
+      <c r="C98" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D98" s="0" t="s">
+      <c r="D98" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E98" s="0" t="s">
+      <c r="E98" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F98" s="0" t="s">
+      <c r="F98" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="H98" s="4" t="n">
+      <c r="H98" s="3" t="n">
         <v>12.85</v>
       </c>
-      <c r="J98" s="0" t="s">
+      <c r="J98" s="2" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C99" s="0" t="n">
+      <c r="C99" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="D99" s="0" t="s">
+      <c r="D99" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="E99" s="0" t="s">
+      <c r="E99" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F99" s="0" t="s">
+      <c r="F99" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="H99" s="4" t="n">
+      <c r="H99" s="3" t="n">
         <v>7.45</v>
       </c>
-      <c r="J99" s="0" t="s">
+      <c r="J99" s="2" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C100" s="0" t="n">
+      <c r="C100" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D100" s="0" t="s">
+      <c r="D100" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E100" s="0" t="s">
+      <c r="E100" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F100" s="0" t="s">
+      <c r="F100" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="H100" s="4" t="n">
+      <c r="H100" s="3" t="n">
         <v>19.85</v>
       </c>
-      <c r="J100" s="0" t="s">
+      <c r="J100" s="2" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C101" s="0" t="n">
+      <c r="C101" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="D101" s="0" t="s">
+      <c r="D101" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E101" s="0" t="s">
+      <c r="E101" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F101" s="0" t="s">
+      <c r="F101" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="H101" s="4" t="n">
+      <c r="H101" s="3" t="n">
         <v>19.85</v>
       </c>
-      <c r="J101" s="0" t="s">
+      <c r="J101" s="2" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C102" s="0" t="n">
+      <c r="C102" s="2" t="n">
         <v>2020</v>
       </c>
-      <c r="D102" s="0" t="s">
+      <c r="D102" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E102" s="0" t="s">
+      <c r="E102" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F102" s="0" t="s">
+      <c r="F102" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="H102" s="4" t="n">
+      <c r="H102" s="3" t="n">
         <v>22.95</v>
       </c>
-      <c r="J102" s="0" t="s">
+      <c r="J102" s="2" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C103" s="0" t="n">
+      <c r="C103" s="2" t="n">
         <v>2016</v>
       </c>
-      <c r="D103" s="0" t="s">
+      <c r="D103" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E103" s="0" t="s">
+      <c r="E103" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F103" s="0" t="s">
+      <c r="F103" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="H103" s="4" t="n">
+      <c r="H103" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="J103" s="0" t="s">
+      <c r="J103" s="2" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C104" s="0" t="n">
+      <c r="C104" s="2" t="n">
         <v>2012</v>
       </c>
-      <c r="D104" s="0" t="s">
+      <c r="D104" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E104" s="0" t="s">
+      <c r="E104" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F104" s="0" t="s">
+      <c r="F104" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="H104" s="4" t="n">
+      <c r="H104" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="J104" s="0" t="s">
+      <c r="J104" s="2" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C105" s="0" t="n">
+      <c r="C105" s="2" t="n">
         <v>2015</v>
       </c>
-      <c r="D105" s="0" t="s">
+      <c r="D105" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E105" s="0" t="s">
+      <c r="E105" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="F105" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="H105" s="4" t="n">
+      <c r="H105" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="J105" s="0" t="s">
+      <c r="J105" s="2" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+      <c r="A106" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C106" s="0" t="n">
+      <c r="C106" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="E106" s="0" t="s">
+      <c r="E106" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F106" s="0" t="s">
+      <c r="F106" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H106" s="4" t="n">
+      <c r="H106" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="J106" s="0" t="s">
+      <c r="J106" s="2" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+      <c r="A107" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C107" s="0" t="n">
+      <c r="C107" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="D107" s="0" t="s">
+      <c r="D107" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E107" s="0" t="s">
+      <c r="E107" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F107" s="0" t="s">
+      <c r="F107" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="H107" s="4" t="n">
+      <c r="H107" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="J107" s="0" t="s">
+      <c r="J107" s="2" t="s">
         <v>307</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="C108" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D108" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="E108" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="F108" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J108" s="0" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="C109" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D109" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E109" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="F109" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J109" s="0" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="C110" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E110" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="F110" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J110" s="0" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="C111" s="0" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E111" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="F111" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J111" s="0" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="C112" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D112" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="E112" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="F112" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="J112" s="0" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="C113" s="0" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D113" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="E113" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F113" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J113" s="0" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="C114" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D114" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="E114" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F114" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="J114" s="0" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="C115" s="0" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D115" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="E115" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F115" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="J115" s="0" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>338</v>
+      </c>
+      <c r="C116" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D116" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="E116" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F116" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="J116" s="0" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="C117" s="0" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D117" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="E117" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F117" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="J117" s="0" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="C118" s="0" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E118" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="F118" s="0" t="s">
+        <v>349</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>18.89</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="J118" s="0" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
